--- a/site/exports/bnu-history.xlsx
+++ b/site/exports/bnu-history.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -452,9 +452,9 @@
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,65 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>汪高鑫</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>历史学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Profile and directory readable. No personal advisor relationship disclosed in retained career section. No inference from doctoral-supervisor job label about own advisor.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；NEW_RECOVERY：基于留存公开职业来源记录重建；必要事实仍有缺项，不代表完整履历或当前人事认证。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：中国史学思想史；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；来源ID：new-recovery-bnu-wanggaoxin-s002-5092f571a59f；https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm | 中国史学思想史专题；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；来源ID：new-recovery-bnu-wanggaoxin-s002-5092f571a59f；https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm | 儒学与传统文化；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；来源ID：new-recovery-bnu-wanggaoxin-s002-5092f571a59f；https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm | 史学名著选读；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；来源ID：new-recovery-bnu-wanggaoxin-s002-5092f571a59f；https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,13 +692,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="23.8" customWidth="1" min="2" max="2"/>
     <col width="26.6" customWidth="1" min="3" max="3"/>
-    <col width="22.4" customWidth="1" min="4" max="4"/>
+    <col width="32.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -720,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1416,8 +1470,303 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>汪高鑫</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>历史学学士学位</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>安徽师范大学</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Explicit 获 supports an award. The stated year modifies graduation; no separate award date or legal issuing entity is asserted.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（毕业年份）：1983</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>汪高鑫</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>历史学硕士学位</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Explicit 获 supports an award. The stated year modifies graduation; no separate award date or legal issuing entity is asserted.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（毕业年份）：1990</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>汪高鑫</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>历史学博士学位</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Explicit 获 supports an award. The stated year modifies graduation; no separate award date or legal issuing entity is asserted.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（毕业年份）：2002</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>汪高鑫</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>教授、博士生导师</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学历史学院、史学理论与史学史研究中心</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Source profile says 现为; no independent current HR confirmation; compound affiliation left as source wording.；任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（机构标签）：北京师范大学历史学院、史学理论与史学史研究中心；来源记载（职务角色）：教授、博士生导师</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>汪高鑫</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>主任</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>《史学史研究》编辑部</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Only source-listed professional role; employment and editorial incumbency are not independently verified.；任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（机构标签）：《史学史研究》编辑部；来源记载（职务角色）：主任</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S12"/>
+  <autoFilter ref="A1:S17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1430,6 +1779,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1532,7 +1886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1835,8 +2189,116 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>汪高鑫</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>中国史学思想史十五讲</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；Selected two official-profile works only. Complete authorship and sole-author status not stated; no publisher lookup.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>汪高鑫</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>中国史学思想史散论</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；Selected two official-profile works only. Complete authorship and sole-author status not stated; no publisher lookup.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1850,6 +2312,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1861,14 +2327,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="29.4" customWidth="1" min="2" max="2"/>
+    <col width="62.99999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2042,13 +2508,89 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>汪高鑫</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-wanggaoxin-s001-6627d726f91b</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://history.bnu.edu.cn/szdw/index.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:03:37.397Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>汪高鑫</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-wanggaoxin-s002-5092f571a59f</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://history.bnu.edu.cn/szdw/4ec92b189fbb4a74b644bb04e013917c.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T21:03:25.394Z</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/bnu-history.xlsx
+++ b/site/exports/bnu-history.xlsx
@@ -1566,7 +1566,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L14" s="2" t="b">
@@ -1629,7 +1629,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L15" s="2" t="b">
